--- a/100_Transformation_PySpark.xlsx
+++ b/100_Transformation_PySpark.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1. Learning\4. Azure_DE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Akshansh Dhama\Desktop\B33_GitTest\AKs_DE_Deploy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C85DF59-E20F-4F77-B396-7D5E1CAC0605}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D564A2-76BD-4837-BC3F-42DC0BC78988}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="9090" xr2:uid="{78008007-F1C5-4B8E-B594-22B02F2AE58F}"/>
   </bookViews>
@@ -25,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="283">
   <si>
     <t>No.</t>
   </si>
   <si>
-    <t>Transformation</t>
-  </si>
-  <si>
     <t>PySpark Script</t>
   </si>
   <si>
@@ -876,22 +873,7 @@
     <t>Month difference</t>
   </si>
   <si>
-    <t>last_day</t>
-  </si>
-  <si>
-    <t>df.withColumn("month_end", last_day(col("joining_date")))</t>
-  </si>
-  <si>
-    <t>Month-end date</t>
-  </si>
-  <si>
-    <t>next_day</t>
-  </si>
-  <si>
-    <t>df.withColumn("next_monday", next_day(col("joining_date"), "Mon"))</t>
-  </si>
-  <si>
-    <t>Next Monday</t>
+    <t>Transformation_Details</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8869A3-9F67-4DF5-A86B-755429034432}">
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="5" bestFit="1" customWidth="1"/>
@@ -1280,13 +1262,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1294,13 +1276,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>5</v>
       </c>
       <c r="E2" t="str">
         <f>"## "&amp;C2</f>
@@ -1312,13 +1294,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E66" si="0">"## "&amp;C3</f>
@@ -1330,13 +1312,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
@@ -1348,13 +1330,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
@@ -1366,13 +1348,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -1384,13 +1366,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -1402,13 +1384,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -1420,13 +1402,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -1438,13 +1420,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -1456,13 +1438,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -1474,13 +1456,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
@@ -1492,13 +1474,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
@@ -1510,13 +1492,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
@@ -1528,13 +1510,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="E15" t="str">
         <f t="shared" si="0"/>
@@ -1546,13 +1528,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" si="0"/>
@@ -1564,13 +1546,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="E17" t="str">
         <f t="shared" si="0"/>
@@ -1582,13 +1564,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="E18" t="str">
         <f t="shared" si="0"/>
@@ -1600,13 +1582,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
@@ -1618,13 +1600,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -1636,13 +1618,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" si="0"/>
@@ -1654,13 +1636,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="0"/>
@@ -1672,13 +1654,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="E23" t="str">
         <f t="shared" si="0"/>
@@ -1690,13 +1672,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="E24" t="str">
         <f t="shared" si="0"/>
@@ -1708,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="E25" t="str">
         <f t="shared" si="0"/>
@@ -1726,13 +1708,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E26" t="str">
         <f t="shared" si="0"/>
@@ -1744,13 +1726,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="E27" t="str">
         <f t="shared" si="0"/>
@@ -1762,13 +1744,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="E28" t="str">
         <f t="shared" si="0"/>
@@ -1780,13 +1762,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="E29" t="str">
         <f t="shared" si="0"/>
@@ -1798,13 +1780,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="E30" t="str">
         <f t="shared" si="0"/>
@@ -1816,13 +1798,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="E31" t="str">
         <f t="shared" si="0"/>
@@ -1834,13 +1816,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="E32" t="str">
         <f t="shared" si="0"/>
@@ -1852,13 +1834,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="E33" t="str">
         <f t="shared" si="0"/>
@@ -1870,13 +1852,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="E34" t="str">
         <f t="shared" si="0"/>
@@ -1888,13 +1870,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="E35" t="str">
         <f t="shared" si="0"/>
@@ -1906,13 +1888,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="E36" t="str">
         <f t="shared" si="0"/>
@@ -1924,13 +1906,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="E37" t="str">
         <f t="shared" si="0"/>
@@ -1942,13 +1924,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="E38" t="str">
         <f t="shared" si="0"/>
@@ -1960,13 +1942,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="E39" t="str">
         <f t="shared" si="0"/>
@@ -1978,13 +1960,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="E40" t="str">
         <f t="shared" si="0"/>
@@ -1996,13 +1978,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="E41" t="str">
         <f t="shared" si="0"/>
@@ -2014,13 +1996,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="E42" t="str">
         <f t="shared" si="0"/>
@@ -2032,13 +2014,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="E43" t="str">
         <f t="shared" si="0"/>
@@ -2050,13 +2032,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="E44" t="str">
         <f t="shared" si="0"/>
@@ -2068,13 +2050,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="E45" t="str">
         <f t="shared" si="0"/>
@@ -2086,13 +2068,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="E46" t="str">
         <f t="shared" si="0"/>
@@ -2104,13 +2086,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="E47" t="str">
         <f t="shared" si="0"/>
@@ -2122,13 +2104,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="E48" t="str">
         <f t="shared" si="0"/>
@@ -2140,13 +2122,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="E49" t="str">
         <f t="shared" si="0"/>
@@ -2158,13 +2140,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="E50" t="str">
         <f t="shared" si="0"/>
@@ -2176,13 +2158,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="E51" t="str">
         <f t="shared" si="0"/>
@@ -2194,13 +2176,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="E52" t="str">
         <f t="shared" si="0"/>
@@ -2212,13 +2194,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="E53" t="str">
         <f t="shared" si="0"/>
@@ -2230,13 +2212,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="E54" t="str">
         <f t="shared" si="0"/>
@@ -2248,13 +2230,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="E55" t="str">
         <f t="shared" si="0"/>
@@ -2266,13 +2248,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="E56" t="str">
         <f t="shared" si="0"/>
@@ -2284,13 +2266,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="E57" t="str">
         <f t="shared" si="0"/>
@@ -2302,13 +2284,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="E58" t="str">
         <f t="shared" si="0"/>
@@ -2320,13 +2302,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="E59" t="str">
         <f t="shared" si="0"/>
@@ -2338,13 +2320,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="E60" t="str">
         <f t="shared" si="0"/>
@@ -2356,13 +2338,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="E61" t="str">
         <f t="shared" si="0"/>
@@ -2374,13 +2356,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="E62" t="str">
         <f t="shared" si="0"/>
@@ -2392,13 +2374,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D63" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="E63" t="str">
         <f t="shared" si="0"/>
@@ -2410,13 +2392,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="E64" t="str">
         <f t="shared" si="0"/>
@@ -2428,13 +2410,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="E65" t="str">
         <f t="shared" si="0"/>
@@ -2446,13 +2428,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="E66" t="str">
         <f t="shared" si="0"/>
@@ -2464,16 +2446,16 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>187</v>
-      </c>
       <c r="E67" t="str">
-        <f t="shared" ref="E67:E101" si="1">"## "&amp;C67</f>
+        <f t="shared" ref="E67:E99" si="1">"## "&amp;C67</f>
         <v>## Proper case</v>
       </c>
     </row>
@@ -2482,13 +2464,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C68" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="E68" t="str">
         <f t="shared" si="1"/>
@@ -2500,13 +2482,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="E69" t="str">
         <f t="shared" si="1"/>
@@ -2518,13 +2500,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="E70" t="str">
         <f t="shared" si="1"/>
@@ -2536,13 +2518,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="E71" t="str">
         <f t="shared" si="1"/>
@@ -2554,13 +2536,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="E72" t="str">
         <f t="shared" si="1"/>
@@ -2572,13 +2554,13 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="E73" t="str">
         <f t="shared" si="1"/>
@@ -2590,13 +2572,13 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="E74" t="str">
         <f t="shared" si="1"/>
@@ -2608,13 +2590,13 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="E75" t="str">
         <f t="shared" si="1"/>
@@ -2626,13 +2608,13 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="E76" t="str">
         <f t="shared" si="1"/>
@@ -2644,13 +2626,13 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="E77" t="str">
         <f t="shared" si="1"/>
@@ -2662,13 +2644,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="E78" t="str">
         <f t="shared" si="1"/>
@@ -2680,13 +2662,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="E79" t="str">
         <f t="shared" si="1"/>
@@ -2698,13 +2680,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="E80" t="str">
         <f t="shared" si="1"/>
@@ -2716,13 +2698,13 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>227</v>
       </c>
       <c r="E81" t="str">
         <f t="shared" si="1"/>
@@ -2734,13 +2716,13 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D82" s="2" t="s">
         <v>229</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>230</v>
       </c>
       <c r="E82" t="str">
         <f t="shared" si="1"/>
@@ -2752,13 +2734,13 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="E83" t="str">
         <f t="shared" si="1"/>
@@ -2770,13 +2752,13 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D84" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>236</v>
       </c>
       <c r="E84" t="str">
         <f t="shared" si="1"/>
@@ -2788,13 +2770,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="E85" t="str">
         <f t="shared" si="1"/>
@@ -2806,13 +2788,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D86" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="E86" t="str">
         <f t="shared" si="1"/>
@@ -2824,13 +2806,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D87" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="E87" t="str">
         <f t="shared" si="1"/>
@@ -2842,13 +2824,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="E88" t="str">
         <f t="shared" si="1"/>
@@ -2860,13 +2842,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>251</v>
       </c>
       <c r="E89" t="str">
         <f t="shared" si="1"/>
@@ -2878,13 +2860,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="E90" t="str">
         <f t="shared" si="1"/>
@@ -2896,13 +2878,13 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="E91" t="str">
         <f t="shared" si="1"/>
@@ -2914,13 +2896,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="E92" t="str">
         <f t="shared" si="1"/>
@@ -2932,13 +2914,13 @@
         <v>92</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="E93" t="str">
         <f t="shared" si="1"/>
@@ -2950,13 +2932,13 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D94" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="E94" t="str">
         <f t="shared" si="1"/>
@@ -2968,13 +2950,13 @@
         <v>94</v>
       </c>
       <c r="B95" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="E95" t="str">
         <f t="shared" si="1"/>
@@ -2986,13 +2968,13 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="E96" t="str">
         <f t="shared" si="1"/>
@@ -3004,13 +2986,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="E97" t="str">
         <f t="shared" si="1"/>
@@ -3022,13 +3004,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="E98" t="str">
         <f t="shared" si="1"/>
@@ -3040,53 +3022,17 @@
         <v>98</v>
       </c>
       <c r="B99" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>281</v>
-      </c>
       <c r="E99" t="str">
         <f t="shared" si="1"/>
         <v>## Month difference</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="4">
-        <v>99</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E100" t="str">
-        <f t="shared" si="1"/>
-        <v>## Month-end date</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="4">
-        <v>100</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="E101" t="str">
-        <f t="shared" si="1"/>
-        <v>## Next Monday</v>
       </c>
     </row>
   </sheetData>
